--- a/Excel/VENETIAN-NEW.xlsx
+++ b/Excel/VENETIAN-NEW.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC317AD-3DE0-4CA0-A672-D9BF4FCB7A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D5EF1A-E4EB-44FD-BB70-4E37BF857FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{96D017A1-09C2-4819-905B-1CA7A3E2C82B}"/>
   </bookViews>
@@ -240,7 +240,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,6 +418,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -581,8 +587,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -938,36 +945,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA86FB2-80B0-45F2-A58F-6E0C80A8D397}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -983,66 +990,66 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>16</v>
       </c>
     </row>
